--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487421_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487421_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8882</v>
+        <v>6.4756</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4111</v>
+        <v>4.2659</v>
       </c>
       <c r="F2" t="n">
-        <v>2.477</v>
+        <v>2.2097</v>
       </c>
       <c r="G2" t="n">
         <v>3.2783</v>
@@ -610,13 +610,13 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3564</v>
+        <v>-0.0562</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1411</v>
+        <v>-0.0041</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2153</v>
+        <v>-0.052</v>
       </c>
       <c r="V2" t="n">
         <v>1.8825</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8478</v>
+        <v>6.0714</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0897</v>
+        <v>3.6607</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7582</v>
+        <v>2.4107</v>
       </c>
       <c r="G3" t="n">
         <v>1.8435</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0164</v>
+        <v>0.2072</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8557</v>
+        <v>-0.2847</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8393</v>
+        <v>0.4918</v>
       </c>
       <c r="V3" t="n">
         <v>3.0415</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7067</v>
+        <v>3.9153</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0532</v>
+        <v>1.0103</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6535</v>
+        <v>2.905</v>
       </c>
       <c r="G4" t="n">
         <v>2.3017</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5801</v>
+        <v>0.7887</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0641</v>
+        <v>0.0212</v>
       </c>
       <c r="U4" t="n">
-        <v>1.516</v>
+        <v>0.7675</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4712</v>
+        <v>2.6048</v>
       </c>
       <c r="E5" t="n">
         <v>1.5027</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9685</v>
+        <v>1.1021</v>
       </c>
       <c r="G5" t="n">
         <v>3.3787</v>
@@ -844,13 +844,13 @@
         <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6702</v>
+        <v>-0.5365</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1012</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.569</v>
+        <v>-0.4354</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2166</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CACHON VILLAMEDIANA</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8365</v>
+        <v>1.6053</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7583</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0782</v>
+        <v>0.6309</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6688</v>
+        <v>2.3379</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0422</v>
+        <v>-0.5212</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3734</v>
+        <v>2.8591</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2283</v>
+        <v>2.1858</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0546</v>
+        <v>-0.2535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2829</v>
+        <v>2.4394</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4405</v>
+        <v>0.152</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0968</v>
+        <v>-0.2677</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6563</v>
+        <v>0.4197</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3208</v>
+        <v>-0.8709</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6452</v>
+        <v>-0.1747</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9659</v>
+        <v>-0.6962</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6659</v>
+        <v>-0.0576</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1152</v>
+        <v>-0.0576</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>R. CACHON VILLAMEDIANA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1111</v>
+        <v>1.5433</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6673</v>
+        <v>0.1443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4438</v>
+        <v>1.3989</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3379</v>
+        <v>0.6688</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5212</v>
+        <v>1.0422</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8591</v>
+        <v>-0.3734</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1858</v>
+        <v>0.2283</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2535</v>
+        <v>-0.0546</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4394</v>
+        <v>0.2829</v>
       </c>
       <c r="M7" t="n">
-        <v>0.152</v>
+        <v>0.4405</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2677</v>
+        <v>1.0968</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4197</v>
+        <v>-0.6563</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1751</v>
+        <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.365</v>
+        <v>-0.614</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4817</v>
+        <v>0.0312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8833</v>
+        <v>-0.6452</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0576</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0576</v>
+        <v>-0.1152</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6232</v>
+        <v>1.2801</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0738</v>
+        <v>0.8932</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6969</v>
+        <v>0.387</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1546</v>
+        <v>2.9936</v>
       </c>
       <c r="H8" t="n">
-        <v>3.782</v>
+        <v>2.701</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6274</v>
+        <v>0.2925</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7204</v>
+        <v>2.027</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6863</v>
+        <v>2.6948</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9659</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4343</v>
+        <v>0.9666</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0957</v>
+        <v>0.0062</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6615</v>
+        <v>0.9603</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3683</v>
+        <v>-1.0844</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1317</v>
+        <v>-0.4299</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>-0.6544</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
         <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6197</v>
+        <v>0.5254</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5268</v>
+        <v>-2.2784</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0929</v>
+        <v>2.8039</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9936</v>
+        <v>1.1546</v>
       </c>
       <c r="H9" t="n">
-        <v>2.701</v>
+        <v>3.782</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2925</v>
+        <v>-2.6274</v>
       </c>
       <c r="J9" t="n">
-        <v>2.027</v>
+        <v>0.7204</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6948</v>
+        <v>2.6863</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-1.9659</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9666</v>
+        <v>0.4343</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0062</v>
+        <v>1.0957</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9603</v>
+        <v>-0.6615</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5875</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7448</v>
+        <v>0.2705</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7963</v>
+        <v>-0.3364</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9485</v>
+        <v>0.607</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="W9" t="n">
         <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1001</v>
+        <v>-0.9176</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0971</v>
+        <v>-0.9948</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.003</v>
+        <v>0.0772</v>
       </c>
       <c r="G10" t="n">
         <v>-0.976</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1305</v>
+        <v>0.313</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.22</v>
+        <v>-0.1176</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3505</v>
+        <v>0.4307</v>
       </c>
       <c r="V10" t="n">
         <v>0.3329</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8085</v>
+        <v>-1.6108</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8155</v>
+        <v>-3.8585</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0071</v>
+        <v>2.2476</v>
       </c>
       <c r="G11" t="n">
         <v>0.0125</v>
@@ -1312,13 +1312,13 @@
         <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3325</v>
+        <v>-0.1348</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3517</v>
+        <v>-0.3946</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0192</v>
+        <v>0.2598</v>
       </c>
       <c r="V11" t="n">
         <v>0.6659</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.1958</v>
+        <v>21.4928</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0227</v>
+        <v>5.319700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>16.1731</v>
+        <v>16.173</v>
       </c>
       <c r="G12" t="n">
         <v>16.9936</v>
@@ -1390,13 +1390,13 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.014399999999999</v>
+        <v>-1.7174</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.0879</v>
+        <v>-1.7908</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07359999999999994</v>
+        <v>0.07359999999999978</v>
       </c>
       <c r="V12" t="n">
         <v>4.258100000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7303</v>
+        <v>2.2914</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1119</v>
+        <v>1.2932</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.9982</v>
       </c>
       <c r="G13" t="n">
         <v>1.1757</v>
@@ -1468,13 +1468,13 @@
         <v>0.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7712</v>
+        <v>0.3323</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9487</v>
+        <v>0.13</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1775</v>
+        <v>0.2023</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0165</v>
+        <v>0.601</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1364</v>
+        <v>0.3411</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1199</v>
+        <v>0.2599</v>
       </c>
       <c r="G14" t="n">
         <v>-0.2488</v>
@@ -1546,13 +1546,13 @@
         <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.184</v>
+        <v>0.4005</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0065</v>
+        <v>0.1982</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1775</v>
+        <v>0.2023</v>
       </c>
       <c r="V14" t="n">
         <v>0.0576</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1303</v>
+        <v>0.4718</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5331</v>
+        <v>-0.1237</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4028</v>
+        <v>0.5955</v>
       </c>
       <c r="G15" t="n">
         <v>0.2766</v>
@@ -1624,13 +1624,13 @@
         <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3505</v>
+        <v>0.2516</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0228</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6723</v>
+        <v>0.865</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4481</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BLANCO BLANCO</t>
+          <t>M. CACHOPAS GIL PRATES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7997</v>
+        <v>-1.1237</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0554</v>
+        <v>-2.1141</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7443</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5916</v>
+        <v>-2.2364</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0562</v>
+        <v>-3.7218</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5354</v>
+        <v>1.4853</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5802</v>
+        <v>-1.5187</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5802</v>
+        <v>-2.7052</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.1865</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0114</v>
+        <v>-0.7177</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.476</v>
+        <v>-1.0166</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5354</v>
+        <v>0.2988</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5753</v>
+        <v>0.6208</v>
       </c>
       <c r="T16" t="n">
-        <v>0.504</v>
+        <v>0.2041</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0713</v>
+        <v>0.4167</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CACHOPAS GIL PRATES</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8345</v>
+        <v>-1.7267</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0118</v>
+        <v>-0.3742</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1773</v>
+        <v>-1.3525</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2364</v>
+        <v>-0.8317</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.7218</v>
+        <v>-0.6856</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4853</v>
+        <v>-0.1461</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5187</v>
+        <v>0.234</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.7052</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1865</v>
+        <v>0.2425</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7177</v>
+        <v>-1.0656</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0166</v>
+        <v>-0.677</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2988</v>
+        <v>-0.3886</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.09</v>
+        <v>-0.4411</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3064</v>
+        <v>-0.6081</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3964</v>
+        <v>0.167</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8837</v>
+        <v>-1.8249</v>
       </c>
       <c r="W17" t="n">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0944</v>
+        <v>-1.8247</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6682</v>
+        <v>-2.4562</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5739</v>
+        <v>0.6315</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0724</v>
+        <v>-0.9609</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8155</v>
+        <v>-0.8445</v>
       </c>
       <c r="I18" t="n">
-        <v>0.743</v>
+        <v>-0.1164</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6181</v>
+        <v>0.5755</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3604</v>
+        <v>0.0356</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2577</v>
+        <v>0.5399</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6905</v>
+        <v>-1.5364</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1759</v>
+        <v>-0.8801</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.6563</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9585</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.879</v>
+        <v>-0.1012</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3694</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2483</v>
+        <v>0.2682</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0576</v>
+        <v>0.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0576</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>A. BLANCO BLANCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1111</v>
+        <v>-1.8974</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2719</v>
+        <v>-1.26</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8393</v>
+        <v>-0.6374</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8317</v>
+        <v>-1.5916</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6856</v>
+        <v>-1.0562</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1461</v>
+        <v>-0.5354</v>
       </c>
       <c r="J19" t="n">
-        <v>0.234</v>
+        <v>-0.5802</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.5802</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2425</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0656</v>
+        <v>-1.0114</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.677</v>
+        <v>-0.476</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3886</v>
+        <v>-0.5354</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8255</v>
+        <v>0.4776</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5058</v>
+        <v>0.2994</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3197</v>
+        <v>0.1782</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2242</v>
+        <v>-2.0684</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0532</v>
+        <v>-1.9508</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.171</v>
+        <v>-0.1175</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2957</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3262</v>
+        <v>0.482</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2905</v>
+        <v>0.3929</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2754</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LOPE REBOLLO</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7709</v>
+        <v>-2.5921</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0476</v>
+        <v>-2.7706</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7234</v>
+        <v>0.1785</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0813</v>
+        <v>-1.0724</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9949</v>
+        <v>-1.8155</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0864</v>
+        <v>0.743</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0668</v>
+        <v>1.6181</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2977</v>
+        <v>0.3604</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3645</v>
+        <v>1.2577</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0145</v>
+        <v>-2.6905</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2926</v>
+        <v>-2.1759</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2781</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5875</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3311</v>
+        <v>0.3813</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9985</v>
+        <v>-0.4717</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3327</v>
+        <v>0.8529</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4332</v>
+        <v>0.0576</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4332</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4031</v>
+        <v>-3.2924</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2749</v>
+        <v>-2.9966</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1281</v>
+        <v>-0.2957</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9609</v>
+        <v>-4.7048</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8445</v>
+        <v>-6.2005</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1164</v>
+        <v>1.4957</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5755</v>
+        <v>-2.6205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0356</v>
+        <v>-3.959</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5399</v>
+        <v>1.3385</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5364</v>
+        <v>-2.0843</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8801</v>
+        <v>-2.2415</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6563</v>
+        <v>0.1572</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6795</v>
+        <v>0.1003</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.188</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4914</v>
+        <v>0.7137</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6083</v>
+        <v>0.3329</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3329</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>S. LOPE REBOLLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5708</v>
+        <v>-3.5362</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.406</v>
+        <v>-0.8662</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1649</v>
+        <v>-2.6699</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.7048</v>
+        <v>-2.0813</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.2005</v>
+        <v>-0.9949</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4957</v>
+        <v>-1.0864</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6205</v>
+        <v>-1.0668</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.959</v>
+        <v>0.2977</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3385</v>
+        <v>-1.3645</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0843</v>
+        <v>-1.0145</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.2415</v>
+        <v>-1.2926</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1572</v>
+        <v>0.2781</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9792</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9585</v>
+        <v>0.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1782</v>
+        <v>1.5659</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0228</v>
+        <v>1.1798</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8446</v>
+        <v>0.3861</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3329</v>
+        <v>-2.4332</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8837</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0038</v>
+        <v>-3.7696</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0995</v>
+        <v>-2.8949</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9042</v>
+        <v>-0.8747</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4223</v>
@@ -2326,13 +2326,13 @@
         <v>0.1958</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4392</v>
+        <v>0.6734</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0065</v>
+        <v>0.1982</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4457</v>
+        <v>0.4752</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2166</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.196</v>
+        <v>-18.467</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.1733</v>
+        <v>-16.173</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.0227</v>
+        <v>-2.2937</v>
       </c>
       <c r="G25" t="n">
         <v>-16.9936</v>
@@ -2374,16 +2374,16 @@
         <v>-16.3634</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6305000000000001</v>
+        <v>-0.6305000000000005</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.613799999999999</v>
+        <v>-3.6138</v>
       </c>
       <c r="K25" t="n">
         <v>-4.8225</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2087</v>
+        <v>1.208699999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-13.3798</v>
@@ -2404,13 +2404,13 @@
         <v>12.7301</v>
       </c>
       <c r="S25" t="n">
-        <v>2.0143</v>
+        <v>4.7434</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.07369999999999971</v>
+        <v>-0.07340000000000008</v>
       </c>
       <c r="U25" t="n">
-        <v>2.088</v>
+        <v>4.8167</v>
       </c>
       <c r="V25" t="n">
         <v>-4.2581</v>
